--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomislav\Desktop\rasadnik\rasadnik-bernat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\rasadnik-bernat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05C176B-7995-428F-B94E-A3E77D0F0F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AEF90E-BED0-46F7-AC94-F8C3BACA7B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="contact" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>Pakrani 2, 43500, Pakrani</t>
   </si>
   <si>
-    <t>https://maps.app.goo.gl/AT5BkUW8KtP7cEmT8</t>
-  </si>
-  <si>
     <t>&lt;iframe src="https://www.google.com/maps/embed?pb=!1m18!1m12!1m3!1d2793.2759135682068!2d17.267677576610776!3d45.56488982671428!2m3!1f0!2f0!3f0!3m2!1i1024!2i768!4f13.1!3m3!1m2!1s0x47679ebf8fc10109%3A0x9052e1430e366197!2sPakrani%202%2C%2043500%2C%20Pakrani!5e0!3m2!1sen!2shr!4v1764924698835!5m2!1sen!2shr" width="600" height="450" style="border:0;" allowfullscreen="" loading="lazy" referrerpolicy="no-referrer-when-downgrade"&gt;&lt;/iframe&gt;</t>
   </si>
   <si>
@@ -374,12 +371,15 @@
   <si>
     <t>usluga_sadnje 1.jpg</t>
   </si>
+  <si>
+    <t>https://maps.app.goo.gl/WrfEUjHcn54o7LMY7</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -391,12 +391,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -437,15 +431,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -470,8 +463,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hiperveza" xfId="1" builtinId="8"/>
+    <cellStyle name="Normalno" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -688,16 +681,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="21.85546875" customWidth="1"/>
-    <col min="4" max="4" width="36.28515625" customWidth="1"/>
-    <col min="5" max="5" width="365.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" customWidth="1"/>
+    <col min="4" max="4" width="36.33203125" customWidth="1"/>
+    <col min="5" max="5" width="365.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -714,21 +707,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>18</v>
+        <v>63</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -746,149 +739,149 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" customWidth="1"/>
-    <col min="2" max="2" width="47.140625" customWidth="1"/>
-    <col min="3" max="4" width="170.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="35.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.88671875" customWidth="1"/>
+    <col min="2" max="2" width="47.109375" customWidth="1"/>
+    <col min="3" max="4" width="170.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="194.45" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:6" ht="194.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="186.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="9" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="186.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:6" ht="166.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="B4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="9" t="s">
+      <c r="E4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="166.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="5" spans="1:6" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="E5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="176.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="7" t="s">
+    <row r="6" spans="1:6" ht="158.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="B6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="9" t="s">
+      <c r="E6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="7" spans="1:6" ht="158.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="E7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -902,68 +895,68 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="55.7109375" style="12" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" customWidth="1"/>
-    <col min="6" max="30" width="9.28515625" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" customWidth="1"/>
+    <col min="3" max="4" width="55.6640625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="21.88671875" customWidth="1"/>
+    <col min="6" max="30" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>11</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="363" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="363" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>55</v>
+      <c r="C2" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
       <c r="E5" s="3"/>
     </row>
   </sheetData>
@@ -977,81 +970,81 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="66.42578125" style="12" customWidth="1"/>
-    <col min="4" max="4" width="70.5703125" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="66.44140625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="70.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>11</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D3" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+    <row r="4" spans="1:5" ht="79.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\rasadnik-bernat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7AEF90E-BED0-46F7-AC94-F8C3BACA7B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628A50A5-E803-472D-84F5-C4A699D5D0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\rasadnik-bernat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628A50A5-E803-472D-84F5-C4A699D5D0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE78A84C-D7D0-41FF-9A58-A659B0C1A83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="contact" sheetId="1" r:id="rId1"/>
@@ -115,20 +115,6 @@
   </si>
   <si>
     <t>Informacije o sadnicama:
-- Jednogodišnje sadnice pitomog kestena. Visina sadnica od 20-40cm
-- Dvogodišnje sadnice pitomog kestena. Visina sadnica 60-80cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-Opis vrste:
-- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
-- Plod: jestiv
-- Rodnost: obilna, redovita
-- Vrijeme dozrijevanja: listopad (1.-10.)
-- Oplodnja: potreban oprašivač
-- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
 - Jednogodišnje sadnice pitomog kestena. Visina sadnica od 30-50cm
 - Kontejnerske sadnice
 - Sadnja moguća tijekom cijele godine
@@ -198,20 +184,6 @@
   </si>
   <si>
     <t>Na upit</t>
-  </si>
-  <si>
-    <t>Seedling information:
-- One-year-old sweet chestnut seedlings. Seedling height 20-40cm
-- Two-year-old sweet chestnut seedlings. Seedling height 60-80cm
-- Seedlings are sold bare-root
-- Planting during the dormant season (October-April)
-Species description:
-- Cultivation form: tree, with a lush, large crown.
-- Fruit: edible
-- Yield: abundant, regular
-- Ripening time: October (1-10)
-- Fertilization: pollinator required
-- Soil requirements: pH value from 4.5 to 6.0, must be moderately moist, loose, loamy-sandy texture. Best warm, sunny places, southern, southeastern and eastern exposures</t>
   </si>
   <si>
     <t>Seedling information:
@@ -373,6 +345,34 @@
   </si>
   <si>
     <t>https://maps.app.goo.gl/WrfEUjHcn54o7LMY7</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Jednogodišnje sadnice pitomog kestena. Visina sadnica od 30-40cm
+- Dvogodišnje sadnice pitomog kestena. Visina sadnica 60-80cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
+- Plod: jestiv
+- Rodnost: obilna, redovita
+- Vrijeme dozrijevanja: listopad (1.-10.)
+- Oplodnja: potreban oprašivač
+- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
+  </si>
+  <si>
+    <t>Seedling information:
+- One-year-old sweet chestnut seedlings. Seedling height 30-40cm
+- Two-year-old sweet chestnut seedlings. Seedling height 60-80cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+Species description:
+- Cultivation form: tree, with a lush, large crown.
+- Fruit: edible
+- Yield: abundant, regular
+- Ripening time: October (1-10)
+- Fertilization: pollinator required
+- Soil requirements: pH value from 4.5 to 6.0, must be moderately moist, loose, loamy-sandy texture. Best warm, sunny places, southern, southeastern and eastern exposures</t>
   </si>
 </sst>
 </file>
@@ -709,7 +709,7 @@
     </row>
     <row r="2" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>17</v>
@@ -718,7 +718,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>6</v>
@@ -776,14 +776,14 @@
         <v>19</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="186.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -794,14 +794,14 @@
         <v>21</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="166.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -812,16 +812,16 @@
         <v>23</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -832,56 +832,56 @@
         <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="158.4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="158.4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="F7" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -929,13 +929,13 @@
         <v>15</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.25">
@@ -998,53 +998,53 @@
     </row>
     <row r="2" spans="1:5" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>53</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="C3" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="C4" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\rasadnik-bernat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\Web stranica\Excel za ažuriranje web stranice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE78A84C-D7D0-41FF-9A58-A659B0C1A83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CAF8A5-8EF4-450B-BF54-59FB97E45337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="69">
   <si>
     <t>number</t>
   </si>
@@ -90,65 +90,6 @@
     <t>rasadnikbernat@gmail.com</t>
   </si>
   <si>
-    <t>Kesten pitomi kontejnerske sadnice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweet chestnut (Castanea sativa), bare root </t>
-  </si>
-  <si>
-    <t>Kesten pitomi, golog korjena</t>
-  </si>
-  <si>
-    <t>Sweet chestnut (Castanea sativa), container seedlings</t>
-  </si>
-  <si>
-    <t>Crvenolisni hrast, golog korjena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red Oak ( Quercus rubra), bare root </t>
-  </si>
-  <si>
-    <t>Crvenolisni hrast, kontejnerske sadnice</t>
-  </si>
-  <si>
-    <t>Red Oak ( Quercus rubra), container seedlings</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-- Jednogodišnje sadnice pitomog kestena. Visina sadnica od 30-50cm
-- Kontejnerske sadnice
-- Sadnja moguća tijekom cijele godine
-Opis vrste:
-- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
-- Plod: jestiv
-- Rodnost: obilna, redovita
-- Vrijeme dozrijevanja: listopad (1.-10.)
-- Oplodnja: potreban oprašivač
-- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-- Jednogodišnje sadnice crvenog hrasta. Visina sadnica od 30-50cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-Opis vrste:
-- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
-- Ne stvara alergene.
-- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
-- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-- Jednogodišnje sadnice crvenog hrasta. Visina sadnica od 30-50cm
-- Kontejnerske sadnice
-- Sadnja moguća tijekom cijele godine
-Opis vrste:
-- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
-- Ne stvara alergene.
-- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
-- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
-  </si>
-  <si>
     <t>Hrast lužnjak</t>
   </si>
   <si>
@@ -161,88 +102,7 @@
     <t>Sessile oak (Quercus petraea)</t>
   </si>
   <si>
-    <t>Informacije o sadnicama:
-U ponudi: 
-- jednogodišnje sadnice hrasta lužnjaka (Quercus robur). Visina sadnica od 30-50cm
-- Dvogodišnje sadnice. Visina 70-90cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-Opis vrste:
-- Listopadno stablo iz porodice bukva (Fagaceae). Naraste 40-50 m visine, deblo je promjera do 3 metra. Korijenov sustav je dobro razvijen, dubok, u početku jakog glavnog korijena, kasnije se razvijaju bočne žile. Krošnja je široka, vrlo dobro razgranata, nepravilna, grane su jake i debele, vodoravno stršeće.  
-- Stanište: Odgovaraju mu duboka i plodna, vlažna tla bogata vapnencem.   Otporan je na sušu i visoke temperature, na vjetar i gradska onečišćenja. Teško uspijeva na plitkom i suhom zemljištu, na tlima kisele reakcije i osjetljiv je na kasne mrazeve.</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-U ponudi: 
-- Jednogodišnje sadnice hrasta kitnjaka (Quercus petraea). Visina sadnica od 30-50cm
-- Dvogodišnje sadnice. Visina 70-90cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-Opis vrste: 
-- Listopadno stablo iz porodice bukva (Fagaceae). Stablo naraste do 40 metara visine tvoreći bogato razgranatu, gustu i pravilnu krošnju. Korijenov sustav je dobro razvijen, s jakim središnjim korijenom. Deblo je promjera do 3 metra.
-- Stanište: Raste u brdskoplaninskim područjima, često zajedno uz obični grab, pitomi kesten ili bukvu. Raste od nizina do 1300 m nadmorske visine. Razmnožava se sjemenom koje brzo klija. Skromnih je zahtjeva prema staništu, odgovaraju mu svježa zemljišta, slabije uspijeva na tlu kisele reakcije.</t>
-  </si>
-  <si>
     <t>Na upit</t>
-  </si>
-  <si>
-    <t>Seedling information:
-- One-year-old sweet chestnut seedlings. Seedling height 30-50cm
-- Container seedlings
-- Planting possible throughout the year
-Species description:
-- Cultivation form: tree, with a lush, large crown.
-- Fruit: edible
-- Yield: abundant, regular
-- Ripening time: October (1-10)
-- Fertilization: pollinator required
-- Soil requirements: pH value from 4.5 to 6.0, must be moderately moist, loose, loamy-sandy texture. Best warm, sunny places, southern, southeastern and eastern exposures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-660
-'Seedling information:
-- One-year-old red oak seedlings. Seedling height 30-50cm
-- Seedlings are sold bare-root
-- Planting during the dormant season (October-April)
-Species description:
-- Cultivation form: ornamental tree, with a lush, large crown.
-- Does not produce allergens.
-- Attractive deciduous tree known for its rapid growth and beautiful red color of leaves in autumn.
-- Habitat: The tree is resistant to low temperatures and urban pollution. It is relatively fast-growing, tolerates shade, tolerates most soils, thrives on poor and acidic soils, and is suitable for sandy and fresh soil. It does not tolerate flooded or dry habitats.</t>
-  </si>
-  <si>
-    <t>Seedling information:
-- One-year-old red oak seedlings. Seedling height 30-50cm
-- Container seedlings
-- Planting possible throughout the year
-Species description:
-- Cultivation form: ornamental tree, with a lush, large crown.
-- Does not produce allergens.
-- Attractive deciduous tree known for its rapid growth and beautiful red color of leaves in autumn.
-- Habitat: The tree is resistant to low temperatures and urban pollution. It is relatively fast-growing, tolerates shade, tolerates most soils, thrives on poor soils and acidic soils, and sandy and fresh soil is suitable for it. It does not tolerate flooded or dry habitats.</t>
-  </si>
-  <si>
-    <t>Seedling information:
-On offer:
-- one-year-old pedunculate oak seedlings (Quercus robur). Seedling height 30-50cm
-- two-year-old seedlings. Height 70-90cm
-- Seedlings are sold bare-root
-- Planting during the dormant season (October-April)
-Species description:
-- Deciduous tree from the beech family (Fagaceae). It grows 40-50 m tall, the trunk is up to 3 meters in diameter. The root system is well developed, deep, initially with a strong main root, later lateral veins develop. The crown is wide, very well branched, irregular, the branches are strong and thick, horizontally protruding.
-- Habitat: It is suitable for deep and fertile, moist soils rich in limestone. It is resistant to drought and high temperatures, wind and urban pollution. It has difficulty growing in shallow and dry soil, on acidic soils, and is sensitive to late frosts.</t>
-  </si>
-  <si>
-    <t>Seedling information:
-On offer:
-- One-year-old sessile oak seedlings (Quercus petraea). Seedling height 30-50cm
-- Two-year-old seedlings. Height 70-90cm
-- Seedlings are sold bare-root
-- Planting during the dormant season (October-April)
-Species description:
-- Deciduous tree from the beech family (Fagaceae). The tree grows up to 40 meters tall, forming a richly branched, dense and regular crown. The root system is well developed, with a strong central root. The trunk is up to 3 meters in diameter.
-- Habitat: It grows in hilly and mountainous areas, often together with common hornbeam, sweet chestnut or beech. It grows from lowlands to 1300 m above sea level. It reproduces by seeds that germinate quickly. It has modest requirements for habitat, it is suitable for fresh soils, it does not thrive well on acidic soils.</t>
   </si>
   <si>
     <t>Vršimo uslugu konverzije vaše zapuštene poljoprivredne parcele iz degradiranog, zaraslog zemljišta u šumu. 
@@ -314,15 +174,9 @@
     <t>kesten_golog_korjena</t>
   </si>
   <si>
-    <t>kesten_kontejnerska_sadnica</t>
-  </si>
-  <si>
     <t>crvenolisni_hrast_golog_korjena</t>
   </si>
   <si>
-    <t>crvenolisni_hrast_kontejnerska_sadnica</t>
-  </si>
-  <si>
     <t>hrast_luznjak_golog_korjena</t>
   </si>
   <si>
@@ -347,9 +201,20 @@
     <t>https://maps.app.goo.gl/WrfEUjHcn54o7LMY7</t>
   </si>
   <si>
+    <t>Kesten pitomi, golog korjena 40-70cm</t>
+  </si>
+  <si>
+    <t>Sweet chestnut (Castanea sativa), bare root 40-70cm</t>
+  </si>
+  <si>
+    <t>Kesten pitomi, golog korjena 70-100cm</t>
+  </si>
+  <si>
+    <t>Sweet chestnut (Castanea sativa), bare root 70-100cm</t>
+  </si>
+  <si>
     <t>Informacije o sadnicama:
-- Jednogodišnje sadnice pitomog kestena. Visina sadnica od 30-40cm
-- Dvogodišnje sadnice pitomog kestena. Visina sadnica 60-80cm
+- Visina sadnica 40-70 cm
 - Sadnice se prodaju golog korjena
 - Sadnja tijekom mirovanja vegetacije (listopad-travanj)
 Opis vrste:
@@ -361,9 +226,21 @@
 - Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
   </si>
   <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica 70-100 cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
+- Plod: jestiv
+- Rodnost: obilna, redovita
+- Vrijeme dozrijevanja: listopad (1.-10.)
+- Oplodnja: potreban oprašivač
+- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
+  </si>
+  <si>
     <t>Seedling information:
-- One-year-old sweet chestnut seedlings. Seedling height 30-40cm
-- Two-year-old sweet chestnut seedlings. Seedling height 60-80cm
+- Seedling height 70-100 cm
 - Seedlings are sold bare-root
 - Planting during the dormant season (October-April)
 Species description:
@@ -373,6 +250,123 @@
 - Ripening time: October (1-10)
 - Fertilization: pollinator required
 - Soil requirements: pH value from 4.5 to 6.0, must be moderately moist, loose, loamy-sandy texture. Best warm, sunny places, southern, southeastern and eastern exposures</t>
+  </si>
+  <si>
+    <t>Seedling information:
+- Seedling height 40-70 cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+Species description:
+- Cultivation form: tree, with a lush, large crown.
+- Fruit: edible
+- Yield: abundant, regular
+- Ripening time: October (1-10)
+- Fertilization: pollinator required
+- Soil requirements: pH value from 4.5 to 6.0, must be moderately moist, loose, loamy-sandy texture. Best warm, sunny places, southern, southeastern and eastern exposures</t>
+  </si>
+  <si>
+    <t>5 EUR</t>
+  </si>
+  <si>
+    <t>7 EUR</t>
+  </si>
+  <si>
+    <t>Crvenolisni hrast, golog korjena 40-60cm</t>
+  </si>
+  <si>
+    <t>Red Oak ( Quercus rubra), bare root 40-60cm</t>
+  </si>
+  <si>
+    <t>Crvenolisni hrast, golog korjena 70-100cm</t>
+  </si>
+  <si>
+    <t>Red Oak ( Quercus rubra), bare root 70-100cm</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica od 40-60cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
+- Ne stvara alergene.
+- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
+- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+'Seedling information:
+- Seedling height 40-60 cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+Species description:
+- Cultivation form: ornamental tree, with a lush, large crown.
+- Does not produce allergens.
+- Attractive deciduous tree known for its rapid growth and beautiful red color of leaves in autumn.
+- Habitat: The tree is resistant to low temperatures and urban pollution. It is relatively fast-growing, tolerates shade, tolerates most soils, thrives on poor and acidic soils, and is suitable for sandy and fresh soil. It does not tolerate flooded or dry habitats.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica od 70-100cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
+- Ne stvara alergene.
+- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
+- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+'Seedling information:
+- One-year-old red oak seedlings. Seedling height 70-100cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+Species description:
+- Cultivation form: ornamental tree, with a lush, large crown.
+- Does not produce allergens.
+- Attractive deciduous tree known for its rapid growth and beautiful red color of leaves in autumn.
+- Habitat: The tree is resistant to low temperatures and urban pollution. It is relatively fast-growing, tolerates shade, tolerates most soils, thrives on poor and acidic soils, and is suitable for sandy and fresh soil. It does not tolerate flooded or dry habitats.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+U ponudi: 
+- Dvogodišnje sadnice hrasta lužnjaka (Quercus robur). Visina sadnica od 30-70cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Listopadno stablo iz porodice bukva (Fagaceae). Naraste 40-50 m visine, deblo je promjera do 3 metra. Korijenov sustav je dobro razvijen, dubok, u početku jakog glavnog korijena, kasnije se razvijaju bočne žile. Krošnja je široka, vrlo dobro razgranata, nepravilna, grane su jake i debele, vodoravno stršeće.  
+- Stanište: Odgovaraju mu duboka i plodna, vlažna tla bogata vapnencem.   Otporan je na sušu i visoke temperature, na vjetar i gradska onečišćenja. Teško uspijeva na plitkom i suhom zemljištu, na tlima kisele reakcije i osjetljiv je na kasne mrazeve.</t>
+  </si>
+  <si>
+    <t>Seedling information:
+On offer:
+- Two-year-old pedunculate oak seedlings (Quercus robur). Seedling height 30-70cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+Species description:
+- Deciduous tree from the beech family (Fagaceae). It grows 40-50 m tall, the trunk is up to 3 meters in diameter. The root system is well developed, deep, initially with a strong main root, later lateral veins develop. The crown is wide, very well branched, irregular, the branches are strong and thick, horizontally protruding.
+- Habitat: It is suitable for deep and fertile, moist soils rich in limestone. It is resistant to drought and high temperatures, wind and urban pollution. It has difficulty growing in shallow and dry soil, on acidic soils, and is sensitive to late frosts.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+U ponudi: 
+- Dvogodišnje sadnice hrasta kitnjaka (Quercus petraea). Visina sadnica od 30-70cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste: 
+- Listopadno stablo iz porodice bukva (Fagaceae). Stablo naraste do 40 metara visine tvoreći bogato razgranatu, gustu i pravilnu krošnju. Korijenov sustav je dobro razvijen, s jakim središnjim korijenom. Deblo je promjera do 3 metra.
+- Stanište: Raste u brdskoplaninskim područjima, često zajedno uz obični grab, pitomi kesten ili bukvu. Raste od nizina do 1300 m nadmorske visine. Razmnožava se sjemenom koje brzo klija. Skromnih je zahtjeva prema staništu, odgovaraju mu svježa zemljišta, slabije uspijeva na tlu kisele reakcije.</t>
+  </si>
+  <si>
+    <t>Seedling information:
+On offer:
+- Two-year-old sessile oak seedlings (Quercus petraea). Seedling height 30-70cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+Species description:
+- Deciduous tree from the beech family (Fagaceae). The tree grows up to 40 meters tall, forming a richly branched, dense and regular crown. The root system is well developed, with a strong central root. The trunk is up to 3 meters in diameter.
+- Habitat: It grows in hilly and mountainous areas, often together with common hornbeam, sweet chestnut or beech. It grows from lowlands to 1300 m above sea level. It reproduces by seeds that germinate quickly. It has modest requirements for habitat, it is suitable for fresh soils, it does not thrive well on acidic soils.</t>
   </si>
 </sst>
 </file>
@@ -433,7 +427,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -444,9 +438,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -709,7 +700,7 @@
     </row>
     <row r="2" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>17</v>
@@ -718,7 +709,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>6</v>
@@ -741,7 +732,7 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.88671875" customWidth="1"/>
+    <col min="1" max="1" width="36.77734375" customWidth="1"/>
     <col min="2" max="2" width="47.109375" customWidth="1"/>
     <col min="3" max="4" width="170.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" customWidth="1"/>
@@ -770,118 +761,122 @@
     </row>
     <row r="2" spans="1:6" ht="194.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>55</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="186.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>26</v>
+        <v>50</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>56</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="166.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>37</v>
+        <v>61</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="158.4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="158.4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +894,7 @@
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="2" width="7.6640625" customWidth="1"/>
-    <col min="3" max="4" width="55.6640625" style="11" customWidth="1"/>
+    <col min="3" max="4" width="55.6640625" style="10" customWidth="1"/>
     <col min="5" max="5" width="21.88671875" customWidth="1"/>
     <col min="6" max="30" width="9.33203125" customWidth="1"/>
   </cols>
@@ -911,10 +906,10 @@
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -928,35 +923,35 @@
       <c r="B2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>52</v>
+      <c r="C2" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>34</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
       <c r="E5" s="3"/>
     </row>
   </sheetData>
@@ -974,8 +969,8 @@
   <cols>
     <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="66.44140625" style="11" customWidth="1"/>
-    <col min="4" max="4" width="70.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.44140625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="70.5546875" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -986,10 +981,10 @@
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -998,53 +993,53 @@
     </row>
     <row r="2" spans="1:5" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\Web stranica\Excel za ažuriranje web stranice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CAF8A5-8EF4-450B-BF54-59FB97E45337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF87B461-5C49-4DE5-A703-36FC996A86D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -213,58 +213,6 @@
     <t>Sweet chestnut (Castanea sativa), bare root 70-100cm</t>
   </si>
   <si>
-    <t>Informacije o sadnicama:
-- Visina sadnica 40-70 cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-Opis vrste:
-- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
-- Plod: jestiv
-- Rodnost: obilna, redovita
-- Vrijeme dozrijevanja: listopad (1.-10.)
-- Oplodnja: potreban oprašivač
-- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-- Visina sadnica 70-100 cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-Opis vrste:
-- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
-- Plod: jestiv
-- Rodnost: obilna, redovita
-- Vrijeme dozrijevanja: listopad (1.-10.)
-- Oplodnja: potreban oprašivač
-- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
-  </si>
-  <si>
-    <t>Seedling information:
-- Seedling height 70-100 cm
-- Seedlings are sold bare-root
-- Planting during the dormant season (October-April)
-Species description:
-- Cultivation form: tree, with a lush, large crown.
-- Fruit: edible
-- Yield: abundant, regular
-- Ripening time: October (1-10)
-- Fertilization: pollinator required
-- Soil requirements: pH value from 4.5 to 6.0, must be moderately moist, loose, loamy-sandy texture. Best warm, sunny places, southern, southeastern and eastern exposures</t>
-  </si>
-  <si>
-    <t>Seedling information:
-- Seedling height 40-70 cm
-- Seedlings are sold bare-root
-- Planting during the dormant season (October-April)
-Species description:
-- Cultivation form: tree, with a lush, large crown.
-- Fruit: edible
-- Yield: abundant, regular
-- Ripening time: October (1-10)
-- Fertilization: pollinator required
-- Soil requirements: pH value from 4.5 to 6.0, must be moderately moist, loose, loamy-sandy texture. Best warm, sunny places, southern, southeastern and eastern exposures</t>
-  </si>
-  <si>
     <t>5 EUR</t>
   </si>
   <si>
@@ -281,29 +229,6 @@
   </si>
   <si>
     <t>Red Oak ( Quercus rubra), bare root 70-100cm</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-- Visina sadnica od 40-60cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-Opis vrste:
-- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
-- Ne stvara alergene.
-- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
-- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-'Seedling information:
-- Seedling height 40-60 cm
-- Seedlings are sold bare-root
-- Planting during the dormant season (October-April)
-Species description:
-- Cultivation form: ornamental tree, with a lush, large crown.
-- Does not produce allergens.
-- Attractive deciduous tree known for its rapid growth and beautiful red color of leaves in autumn.
-- Habitat: The tree is resistant to low temperatures and urban pollution. It is relatively fast-growing, tolerates shade, tolerates most soils, thrives on poor and acidic soils, and is suitable for sandy and fresh soil. It does not tolerate flooded or dry habitats.</t>
   </si>
   <si>
     <t>Informacije o sadnicama:
@@ -330,13 +255,106 @@
   </si>
   <si>
     <t>Informacije o sadnicama:
+- Visina sadnica od 40-60cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
+Opis vrste:
+- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
+- Ne stvara alergene.
+- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
+- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica 70-100 cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
+Opis vrste:
+- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
+- Plod: jestiv
+- Rodnost: obilna, redovita
+- Vrijeme dozrijevanja: listopad (1.-10.)
+- Oplodnja: potreban oprašivač
+- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica 40-70 cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
+Opis vrste:
+- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
+- Plod: jestiv
+- Rodnost: obilna, redovita
+- Vrijeme dozrijevanja: listopad (1.-10.)
+- Oplodnja: potreban oprašivač
+- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
 U ponudi: 
 - Dvogodišnje sadnice hrasta lužnjaka (Quercus robur). Visina sadnica od 30-70cm
 - Sadnice se prodaju golog korjena
 - Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
 Opis vrste:
 - Listopadno stablo iz porodice bukva (Fagaceae). Naraste 40-50 m visine, deblo je promjera do 3 metra. Korijenov sustav je dobro razvijen, dubok, u početku jakog glavnog korijena, kasnije se razvijaju bočne žile. Krošnja je široka, vrlo dobro razgranata, nepravilna, grane su jake i debele, vodoravno stršeće.  
 - Stanište: Odgovaraju mu duboka i plodna, vlažna tla bogata vapnencem.   Otporan je na sušu i visoke temperature, na vjetar i gradska onečišćenja. Teško uspijeva na plitkom i suhom zemljištu, na tlima kisele reakcije i osjetljiv je na kasne mrazeve.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+U ponudi: 
+- Dvogodišnje sadnice hrasta kitnjaka (Quercus petraea). Visina sadnica od 30-70cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
+Opis vrste: 
+- Listopadno stablo iz porodice bukva (Fagaceae). Stablo naraste do 40 metara visine tvoreći bogato razgranatu, gustu i pravilnu krošnju. Korijenov sustav je dobro razvijen, s jakim središnjim korijenom. Deblo je promjera do 3 metra.
+- Stanište: Raste u brdskoplaninskim područjima, često zajedno uz obični grab, pitomi kesten ili bukvu. Raste od nizina do 1300 m nadmorske visine. Razmnožava se sjemenom koje brzo klija. Skromnih je zahtjeva prema staništu, odgovaraju mu svježa zemljišta, slabije uspijeva na tlu kisele reakcije.</t>
+  </si>
+  <si>
+    <t>Seedling information:
+- Seedling height 40-70 cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+- Seedlings with a plant passport and health certificate
+Species description:
+- Cultivation form: tree, with a lush, large crown.
+- Fruit: edible
+- Yield: abundant, regular
+- Ripening time: October (1-10)
+- Fertilization: pollinator required
+- Soil requirements: pH value from 4.5 to 6.0, must be moderately moist, loose, loamy-sandy texture. Best warm, sunny places, southern, southeastern and eastern exposures</t>
+  </si>
+  <si>
+    <t>Seedling information:
+- Seedling height 70-100 cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+- Seedlings with a plant passport and health certificate
+Species description:
+- Cultivation form: tree, with a lush, large crown.
+- Fruit: edible
+- Yield: abundant, regular
+- Ripening time: October (1-10)
+- Fertilization: pollinator required
+- Soil requirements: pH value from 4.5 to 6.0, must be moderately moist, loose, loamy-sandy texture. Best warm, sunny places, southern, southeastern and eastern exposures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+'Seedling information:
+- Seedling height 40-60 cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+- Seedlings with a plant passport and health certificate
+Species description:
+- Cultivation form: ornamental tree, with a lush, large crown.
+- Does not produce allergens.
+- Attractive deciduous tree known for its rapid growth and beautiful red color of leaves in autumn.
+- Habitat: The tree is resistant to low temperatures and urban pollution. It is relatively fast-growing, tolerates shade, tolerates most soils, thrives on poor and acidic soils, and is suitable for sandy and fresh soil. It does not tolerate flooded or dry habitats.</t>
   </si>
   <si>
     <t>Seedling information:
@@ -344,19 +362,10 @@
 - Two-year-old pedunculate oak seedlings (Quercus robur). Seedling height 30-70cm
 - Seedlings are sold bare-root
 - Planting during the dormant season (October-April)
+- Seedlings with a plant passport and health certificate
 Species description:
 - Deciduous tree from the beech family (Fagaceae). It grows 40-50 m tall, the trunk is up to 3 meters in diameter. The root system is well developed, deep, initially with a strong main root, later lateral veins develop. The crown is wide, very well branched, irregular, the branches are strong and thick, horizontally protruding.
 - Habitat: It is suitable for deep and fertile, moist soils rich in limestone. It is resistant to drought and high temperatures, wind and urban pollution. It has difficulty growing in shallow and dry soil, on acidic soils, and is sensitive to late frosts.</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-U ponudi: 
-- Dvogodišnje sadnice hrasta kitnjaka (Quercus petraea). Visina sadnica od 30-70cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-Opis vrste: 
-- Listopadno stablo iz porodice bukva (Fagaceae). Stablo naraste do 40 metara visine tvoreći bogato razgranatu, gustu i pravilnu krošnju. Korijenov sustav je dobro razvijen, s jakim središnjim korijenom. Deblo je promjera do 3 metra.
-- Stanište: Raste u brdskoplaninskim područjima, često zajedno uz obični grab, pitomi kesten ili bukvu. Raste od nizina do 1300 m nadmorske visine. Razmnožava se sjemenom koje brzo klija. Skromnih je zahtjeva prema staništu, odgovaraju mu svježa zemljišta, slabije uspijeva na tlu kisele reakcije.</t>
   </si>
   <si>
     <t>Seedling information:
@@ -364,6 +373,7 @@
 - Two-year-old sessile oak seedlings (Quercus petraea). Seedling height 30-70cm
 - Seedlings are sold bare-root
 - Planting during the dormant season (October-April)
+- Seedlings with a plant passport and health certificate
 Species description:
 - Deciduous tree from the beech family (Fagaceae). The tree grows up to 40 meters tall, forming a richly branched, dense and regular crown. The root system is well developed, with a strong central root. The trunk is up to 3 meters in diameter.
 - Habitat: It grows in hilly and mountainous areas, often together with common hornbeam, sweet chestnut or beech. It grows from lowlands to 1300 m above sea level. It reproduces by seeds that germinate quickly. It has modest requirements for habitat, it is suitable for fresh soils, it does not thrive well on acidic soils.</t>
@@ -767,13 +777,13 @@
         <v>48</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>37</v>
@@ -787,13 +797,13 @@
         <v>50</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>37</v>
@@ -801,19 +811,19 @@
     </row>
     <row r="4" spans="1:6" ht="166.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>38</v>
@@ -821,16 +831,16 @@
     </row>
     <row r="5" spans="1:6" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>22</v>
@@ -839,7 +849,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="172.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -847,10 +857,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>22</v>
@@ -859,7 +869,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="172.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
@@ -867,7 +877,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>68</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\Web stranica\Excel za ažuriranje web stranice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF87B461-5C49-4DE5-A703-36FC996A86D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D3BD83-67D6-4B71-89CB-BAE8AB32CD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="70">
   <si>
     <t>number</t>
   </si>
@@ -201,31 +201,10 @@
     <t>https://maps.app.goo.gl/WrfEUjHcn54o7LMY7</t>
   </si>
   <si>
-    <t>Kesten pitomi, golog korjena 40-70cm</t>
-  </si>
-  <si>
-    <t>Sweet chestnut (Castanea sativa), bare root 40-70cm</t>
-  </si>
-  <si>
-    <t>Kesten pitomi, golog korjena 70-100cm</t>
-  </si>
-  <si>
-    <t>Sweet chestnut (Castanea sativa), bare root 70-100cm</t>
-  </si>
-  <si>
     <t>5 EUR</t>
   </si>
   <si>
     <t>7 EUR</t>
-  </si>
-  <si>
-    <t>Crvenolisni hrast, golog korjena 40-60cm</t>
-  </si>
-  <si>
-    <t>Red Oak ( Quercus rubra), bare root 40-60cm</t>
-  </si>
-  <si>
-    <t>Crvenolisni hrast, golog korjena 70-100cm</t>
   </si>
   <si>
     <t>Red Oak ( Quercus rubra), bare root 70-100cm</t>
@@ -377,6 +356,30 @@
 Species description:
 - Deciduous tree from the beech family (Fagaceae). The tree grows up to 40 meters tall, forming a richly branched, dense and regular crown. The root system is well developed, with a strong central root. The trunk is up to 3 meters in diameter.
 - Habitat: It grows in hilly and mountainous areas, often together with common hornbeam, sweet chestnut or beech. It grows from lowlands to 1300 m above sea level. It reproduces by seeds that germinate quickly. It has modest requirements for habitat, it is suitable for fresh soils, it does not thrive well on acidic soils.</t>
+  </si>
+  <si>
+    <t>Kesten pitomi, 40-70cm</t>
+  </si>
+  <si>
+    <t>Kesten pitomi, 70-100cm</t>
+  </si>
+  <si>
+    <t>Crvenolisni hrast, 40-60cm</t>
+  </si>
+  <si>
+    <t>Crvenolisni hrast, 70-100cm</t>
+  </si>
+  <si>
+    <t>Sweet chestnut (Castanea sativa), 40-70cm</t>
+  </si>
+  <si>
+    <t>Sweet chestnut (Castanea sativa), 70-100cm</t>
+  </si>
+  <si>
+    <t>Red Oak ( Quercus rubra), 40-60cm</t>
+  </si>
+  <si>
+    <t>Red Oak ( Quercus rubra), 70-100cm</t>
   </si>
 </sst>
 </file>
@@ -771,19 +774,19 @@
     </row>
     <row r="2" spans="1:6" ht="194.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>37</v>
@@ -791,19 +794,19 @@
     </row>
     <row r="3" spans="1:6" ht="186.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>37</v>
@@ -811,19 +814,19 @@
     </row>
     <row r="4" spans="1:6" ht="166.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>66</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>38</v>
@@ -831,16 +834,16 @@
     </row>
     <row r="5" spans="1:6" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>22</v>
@@ -857,10 +860,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>22</v>
@@ -877,10 +880,10 @@
         <v>21</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>22</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\Web stranica\Excel za ažuriranje web stranice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D3BD83-67D6-4B71-89CB-BAE8AB32CD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D86654E-EF4B-45C3-A0BE-001B5C4B89B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
   <si>
     <t>number</t>
   </si>
@@ -207,9 +207,6 @@
     <t>7 EUR</t>
   </si>
   <si>
-    <t>Red Oak ( Quercus rubra), bare root 70-100cm</t>
-  </si>
-  <si>
     <t>Informacije o sadnicama:
 - Visina sadnica od 70-100cm
 - Sadnice se prodaju golog korjena
@@ -380,6 +377,9 @@
   </si>
   <si>
     <t>Red Oak ( Quercus rubra), 70-100cm</t>
+  </si>
+  <si>
+    <t>kesten_golog_korjena_40_70</t>
   </si>
 </sst>
 </file>
@@ -774,36 +774,36 @@
     </row>
     <row r="2" spans="1:6" ht="194.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="186.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>48</v>
@@ -814,16 +814,16 @@
     </row>
     <row r="4" spans="1:6" ht="166.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>47</v>
@@ -834,16 +834,16 @@
     </row>
     <row r="5" spans="1:6" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>22</v>
@@ -860,10 +860,10 @@
         <v>20</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>22</v>
@@ -880,10 +880,10 @@
         <v>21</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>22</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\Web stranica\Excel za ažuriranje web stranice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D86654E-EF4B-45C3-A0BE-001B5C4B89B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC213033-A239-4A82-B3B4-755342742F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="83">
   <si>
     <t>number</t>
   </si>
@@ -90,19 +90,10 @@
     <t>rasadnikbernat@gmail.com</t>
   </si>
   <si>
-    <t>Hrast lužnjak</t>
-  </si>
-  <si>
-    <t>Hrast kitnjak</t>
-  </si>
-  <si>
     <t>Pedunculate (Quercus robur)</t>
   </si>
   <si>
     <t>Sessile oak (Quercus petraea)</t>
-  </si>
-  <si>
-    <t>Na upit</t>
   </si>
   <si>
     <t>Vršimo uslugu konverzije vaše zapuštene poljoprivredne parcele iz degradiranog, zaraslog zemljišta u šumu. 
@@ -174,13 +165,7 @@
     <t>kesten_golog_korjena</t>
   </si>
   <si>
-    <t>crvenolisni_hrast_golog_korjena</t>
-  </si>
-  <si>
     <t>hrast_luznjak_golog_korjena</t>
-  </si>
-  <si>
-    <t>hrast_kitnjak_golog_korjena</t>
   </si>
   <si>
     <t>+385 99 245 9299</t>
@@ -380,6 +365,93 @@
   </si>
   <si>
     <t>kesten_golog_korjena_40_70</t>
+  </si>
+  <si>
+    <t>Crvenolisni hrast, 100-140cm</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica od 100-140cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
+- Ne stvara alergene.
+- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
+- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+'Seedling information:
+- One-year-old red oak seedlings. Seedling height 100-140cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+Species description:
+- Cultivation form: ornamental tree, with a lush, large crown.
+- Does not produce allergens.
+- Attractive deciduous tree known for its rapid growth and beautiful red color of leaves in autumn.
+- Habitat: The tree is resistant to low temperatures and urban pollution. It is relatively fast-growing, tolerates shade, tolerates most soils, thrives on poor and acidic soils, and is suitable for sandy and fresh soil. It does not tolerate flooded or dry habitats.</t>
+  </si>
+  <si>
+    <t>9 EUR</t>
+  </si>
+  <si>
+    <t>15 EUR</t>
+  </si>
+  <si>
+    <t>crvenolisni_hrast_golog_korjena_70_100</t>
+  </si>
+  <si>
+    <t>Red Oak ( Quercus rubra), 100-140cm</t>
+  </si>
+  <si>
+    <t>crvenolisni_hrast_golog_korjena_100_140</t>
+  </si>
+  <si>
+    <t>crvenolisni_hrast_golog_korjena_40_60</t>
+  </si>
+  <si>
+    <t>Hrast lužnjak 30-70cm</t>
+  </si>
+  <si>
+    <t>Hrast kitnjak 30-70cm</t>
+  </si>
+  <si>
+    <t>Hrast kitnjak 100-150cm</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+U ponudi: 
+- sadnice hrasta kitnjaka (Quercus petraea). Visina sadnica od 100-150cm
+- Sadnice se prodaju golog korjena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
+Opis vrste: 
+- Listopadno stablo iz porodice bukva (Fagaceae). Stablo naraste do 40 metara visine tvoreći bogato razgranatu, gustu i pravilnu krošnju. Korijenov sustav je dobro razvijen, s jakim središnjim korijenom. Deblo je promjera do 3 metra.
+- Stanište: Raste u brdskoplaninskim područjima, često zajedno uz obični grab, pitomi kesten ili bukvu. Raste od nizina do 1300 m nadmorske visine. Razmnožava se sjemenom koje brzo klija. Skromnih je zahtjeva prema staništu, odgovaraju mu svježa zemljišta, slabije uspijeva na tlu kisele reakcije.</t>
+  </si>
+  <si>
+    <t>Seedling information:
+On offer:
+- Sessile oak seedlings (Quercus petraea). Seedling height 100-150cm
+- Seedlings are sold bare-root
+- Planting during the dormant season (October-April)
+- Seedlings with a plant passport and health certificate
+Species description:
+- Deciduous tree from the beech family (Fagaceae). The tree grows up to 40 meters tall, forming a richly branched, dense and regular crown. The root system is well developed, with a strong central root. The trunk is up to 3 meters in diameter.
+- Habitat: It grows in hilly and mountainous areas, often together with common hornbeam, sweet chestnut or beech. It grows from lowlands to 1300 m above sea level. It reproduces by seeds that germinate quickly. It has modest requirements for habitat, it is suitable for fresh soils, it does not thrive well on acidic soils.</t>
+  </si>
+  <si>
+    <t>hrast_kitnjak_golog_korjena_30_70</t>
+  </si>
+  <si>
+    <t>hrast_kitnjak_golog_korjena_100_150</t>
+  </si>
+  <si>
+    <t>2 EUR</t>
+  </si>
+  <si>
+    <t>6 EUR</t>
   </si>
 </sst>
 </file>
@@ -713,7 +785,7 @@
     </row>
     <row r="2" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>17</v>
@@ -722,7 +794,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>6</v>
@@ -742,14 +814,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.77734375" customWidth="1"/>
     <col min="2" max="2" width="47.109375" customWidth="1"/>
     <col min="3" max="4" width="170.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="35.6640625" customWidth="1"/>
+    <col min="6" max="6" width="45.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -774,122 +846,162 @@
     </row>
     <row r="2" spans="1:6" ht="194.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="186.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="166.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="F5" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="172.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="172.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="172.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="172.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="D8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="172.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>40</v>
+      <c r="C9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -937,13 +1049,13 @@
         <v>15</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="99" customHeight="1" x14ac:dyDescent="0.25">
@@ -1006,53 +1118,53 @@
     </row>
     <row r="2" spans="1:5" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\Web stranica\Excel za ažuriranje web stranice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC213033-A239-4A82-B3B4-755342742F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C81F1EA-ED0B-4F32-9141-A174E53E19AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -448,17 +448,59 @@
     <t>hrast_kitnjak_golog_korjena_100_150</t>
   </si>
   <si>
-    <t>2 EUR</t>
-  </si>
-  <si>
-    <t>6 EUR</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TRENUTNO NEDOSTUPNO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2 EUR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TRENUTNO NEDOSTUPNO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+6 EUR</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -476,6 +518,22 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -512,7 +570,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -536,6 +594,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -820,7 +881,7 @@
     <col min="1" max="1" width="36.77734375" customWidth="1"/>
     <col min="2" max="2" width="47.109375" customWidth="1"/>
     <col min="3" max="4" width="170.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.88671875" customWidth="1"/>
     <col min="6" max="6" width="45.109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -957,7 +1018,7 @@
       <c r="D7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="12" t="s">
         <v>81</v>
       </c>
       <c r="F7" s="7" t="s">
@@ -977,7 +1038,7 @@
       <c r="D8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="12" t="s">
         <v>81</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -997,7 +1058,7 @@
       <c r="D9" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="12" t="s">
         <v>82</v>
       </c>
       <c r="F9" s="7" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\Web stranica\Excel za ažuriranje web stranice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C81F1EA-ED0B-4F32-9141-A174E53E19AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E97E75-B73B-427A-AD6B-BD4D2C320F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
   <si>
     <t>number</t>
   </si>
@@ -448,59 +448,14 @@
     <t>hrast_kitnjak_golog_korjena_100_150</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>TRENUTNO NEDOSTUPNO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2 EUR</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>TRENUTNO NEDOSTUPNO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-6 EUR</t>
-    </r>
+    <t>TRENUTNO NEDOSTUPNO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -523,14 +478,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="238"/>
@@ -595,7 +542,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1059,7 +1006,7 @@
         <v>78</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>80</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\Web stranica\Excel za ažuriranje web stranice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E97E75-B73B-427A-AD6B-BD4D2C320F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6454B44D-4565-4192-B39E-A48EDCD5FC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -192,17 +192,6 @@
     <t>7 EUR</t>
   </si>
   <si>
-    <t>Informacije o sadnicama:
-- Visina sadnica od 70-100cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-Opis vrste:
-- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
-- Ne stvara alergene.
-- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
-- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 'Seedling information:
 - One-year-old red oak seedlings. Seedling height 70-100cm
@@ -213,68 +202,6 @@
 - Does not produce allergens.
 - Attractive deciduous tree known for its rapid growth and beautiful red color of leaves in autumn.
 - Habitat: The tree is resistant to low temperatures and urban pollution. It is relatively fast-growing, tolerates shade, tolerates most soils, thrives on poor and acidic soils, and is suitable for sandy and fresh soil. It does not tolerate flooded or dry habitats.</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-- Visina sadnica od 40-60cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
-Opis vrste:
-- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
-- Ne stvara alergene.
-- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
-- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-- Visina sadnica 70-100 cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
-Opis vrste:
-- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
-- Plod: jestiv
-- Rodnost: obilna, redovita
-- Vrijeme dozrijevanja: listopad (1.-10.)
-- Oplodnja: potreban oprašivač
-- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-- Visina sadnica 40-70 cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
-Opis vrste:
-- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
-- Plod: jestiv
-- Rodnost: obilna, redovita
-- Vrijeme dozrijevanja: listopad (1.-10.)
-- Oplodnja: potreban oprašivač
-- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-U ponudi: 
-- Dvogodišnje sadnice hrasta lužnjaka (Quercus robur). Visina sadnica od 30-70cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
-Opis vrste:
-- Listopadno stablo iz porodice bukva (Fagaceae). Naraste 40-50 m visine, deblo je promjera do 3 metra. Korijenov sustav je dobro razvijen, dubok, u početku jakog glavnog korijena, kasnije se razvijaju bočne žile. Krošnja je široka, vrlo dobro razgranata, nepravilna, grane su jake i debele, vodoravno stršeće.  
-- Stanište: Odgovaraju mu duboka i plodna, vlažna tla bogata vapnencem.   Otporan je na sušu i visoke temperature, na vjetar i gradska onečišćenja. Teško uspijeva na plitkom i suhom zemljištu, na tlima kisele reakcije i osjetljiv je na kasne mrazeve.</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-U ponudi: 
-- Dvogodišnje sadnice hrasta kitnjaka (Quercus petraea). Visina sadnica od 30-70cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
-Opis vrste: 
-- Listopadno stablo iz porodice bukva (Fagaceae). Stablo naraste do 40 metara visine tvoreći bogato razgranatu, gustu i pravilnu krošnju. Korijenov sustav je dobro razvijen, s jakim središnjim korijenom. Deblo je promjera do 3 metra.
-- Stanište: Raste u brdskoplaninskim područjima, često zajedno uz obični grab, pitomi kesten ili bukvu. Raste od nizina do 1300 m nadmorske visine. Razmnožava se sjemenom koje brzo klija. Skromnih je zahtjeva prema staništu, odgovaraju mu svježa zemljišta, slabije uspijeva na tlu kisele reakcije.</t>
   </si>
   <si>
     <t>Seedling information:
@@ -370,17 +297,6 @@
     <t>Crvenolisni hrast, 100-140cm</t>
   </si>
   <si>
-    <t>Informacije o sadnicama:
-- Visina sadnica od 100-140cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-Opis vrste:
-- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
-- Ne stvara alergene.
-- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
-- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 'Seedling information:
 - One-year-old red oak seedlings. Seedling height 100-140cm
@@ -420,17 +336,6 @@
     <t>Hrast kitnjak 100-150cm</t>
   </si>
   <si>
-    <t>Informacije o sadnicama:
-U ponudi: 
-- sadnice hrasta kitnjaka (Quercus petraea). Visina sadnica od 100-150cm
-- Sadnice se prodaju golog korjena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
-Opis vrste: 
-- Listopadno stablo iz porodice bukva (Fagaceae). Stablo naraste do 40 metara visine tvoreći bogato razgranatu, gustu i pravilnu krošnju. Korijenov sustav je dobro razvijen, s jakim središnjim korijenom. Deblo je promjera do 3 metra.
-- Stanište: Raste u brdskoplaninskim područjima, često zajedno uz obični grab, pitomi kesten ili bukvu. Raste od nizina do 1300 m nadmorske visine. Razmnožava se sjemenom koje brzo klija. Skromnih je zahtjeva prema staništu, odgovaraju mu svježa zemljišta, slabije uspijeva na tlu kisele reakcije.</t>
-  </si>
-  <si>
     <t>Seedling information:
 On offer:
 - Sessile oak seedlings (Quercus petraea). Seedling height 100-150cm
@@ -449,6 +354,101 @@
   </si>
   <si>
     <t>TRENUTNO NEDOSTUPNO</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica 40-70 cm
+- Sadnice se prodaju golog korijena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
+Opis vrste:
+- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
+- Plod: jestiv
+- Rodnost: obilna, redovita
+- Vrijeme dozrijevanja: listopad (1.-10.)
+- Oplodnja: potreban oprašivač
+- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica 70-100 cm
+- Sadnice se prodaju golog korijena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
+Opis vrste:
+- Uzgojni oblik: stablo, sa bujnom, velikom krošnjom.
+- Plod: jestiv
+- Rodnost: obilna, redovita
+- Vrijeme dozrijevanja: listopad (1.-10.)
+- Oplodnja: potreban oprašivač
+- Zahtjev za tlom: pH vrijednosti od 4,5 do 6,0, mora biti umjereno vlažno, rastresito, ilovasto-pjeskovite teksture. Najbolja topla, sunčana mjesta, južne, jugoistočne i istočne ekspozicije</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica od 40-60cm
+- Sadnice se prodaju golog korijena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
+Opis vrste:
+- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
+- Ne stvara alergene.
+- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
+- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica od 70-100cm
+- Sadnice se prodaju golog korijena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
+- Ne stvara alergene.
+- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
+- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica od 100-140cm
+- Sadnice se prodaju golog korijena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
+- Ne stvara alergene.
+- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
+- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+U ponudi: 
+- Dvogodišnje sadnice hrasta lužnjaka (Quercus robur). Visina sadnica od 30-70cm
+- Sadnice se prodaju golog korijena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
+Opis vrste:
+- Listopadno stablo iz porodice bukva (Fagaceae). Naraste 40-50 m visine, deblo je promjera do 3 metra. Korijenov sustav je dobro razvijen, dubok, u početku jakog glavnog korijena, kasnije se razvijaju bočne žile. Krošnja je široka, vrlo dobro razgranata, nepravilna, grane su jake i debele, vodoravno stršeće.  
+- Stanište: Odgovaraju mu duboka i plodna, vlažna tla bogata vapnencem.   Otporan je na sušu i visoke temperature, na vjetar i gradska onečišćenja. Teško uspijeva na plitkom i suhom zemljištu, na tlima kisele reakcije i osjetljiv je na kasne mrazeve.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+U ponudi: 
+- Dvogodišnje sadnice hrasta kitnjaka (Quercus petraea). Visina sadnica od 30-70cm
+- Sadnice se prodaju golog korijena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
+Opis vrste: 
+- Listopadno stablo iz porodice bukva (Fagaceae). Stablo naraste do 40 metara visine tvoreći bogato razgranatu, gustu i pravilnu krošnju. Korijenov sustav je dobro razvijen, s jakim središnjim korijenom. Deblo je promjera do 3 metra.
+- Stanište: Raste u brdskoplaninskim područjima, često zajedno uz obični grab, pitomi kesten ili bukvu. Raste od nizina do 1300 m nadmorske visine. Razmnožava se sjemenom koje brzo klija. Skromnih je zahtjeva prema staništu, odgovaraju mu svježa zemljišta, slabije uspijeva na tlu kisele reakcije.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+U ponudi: 
+- sadnice hrasta kitnjaka (Quercus petraea). Visina sadnica od 100-150cm
+- Sadnice se prodaju golog korijena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
+Opis vrste: 
+- Listopadno stablo iz porodice bukva (Fagaceae). Stablo naraste do 40 metara visine tvoreći bogato razgranatu, gustu i pravilnu krošnju. Korijenov sustav je dobro razvijen, s jakim središnjim korijenom. Deblo je promjera do 3 metra.
+- Stanište: Raste u brdskoplaninskim područjima, često zajedno uz obični grab, pitomi kesten ili bukvu. Raste od nizina do 1300 m nadmorske visine. Razmnožava se sjemenom koje brzo klija. Skromnih je zahtjeva prema staništu, odgovaraju mu svježa zemljišta, slabije uspijeva na tlu kisele reakcije.</t>
   </si>
 </sst>
 </file>
@@ -854,36 +854,36 @@
     </row>
     <row r="2" spans="1:6" ht="194.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="186.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>43</v>
@@ -894,79 +894,79 @@
     </row>
     <row r="4" spans="1:6" ht="166.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="176.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="172.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>35</v>
@@ -974,42 +974,42 @@
     </row>
     <row r="8" spans="1:6" ht="172.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="172.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivana\Desktop\OPG\Web stranica\Excel za ažuriranje web stranice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6454B44D-4565-4192-B39E-A48EDCD5FC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8470BFE-BEF1-478C-A953-B3ACA2B5A04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -385,40 +385,6 @@
   </si>
   <si>
     <t>Informacije o sadnicama:
-- Visina sadnica od 40-60cm
-- Sadnice se prodaju golog korijena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
-Opis vrste:
-- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
-- Ne stvara alergene.
-- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
-- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-- Visina sadnica od 70-100cm
-- Sadnice se prodaju golog korijena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-Opis vrste:
-- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
-- Ne stvara alergene.
-- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
-- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
-- Visina sadnica od 100-140cm
-- Sadnice se prodaju golog korijena
-- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
-Opis vrste:
-- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
-- Ne stvara alergene.
-- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
-- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, iodgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
-  </si>
-  <si>
-    <t>Informacije o sadnicama:
 U ponudi: 
 - Dvogodišnje sadnice hrasta lužnjaka (Quercus robur). Visina sadnica od 30-70cm
 - Sadnice se prodaju golog korijena
@@ -449,6 +415,40 @@
 Opis vrste: 
 - Listopadno stablo iz porodice bukva (Fagaceae). Stablo naraste do 40 metara visine tvoreći bogato razgranatu, gustu i pravilnu krošnju. Korijenov sustav je dobro razvijen, s jakim središnjim korijenom. Deblo je promjera do 3 metra.
 - Stanište: Raste u brdskoplaninskim područjima, često zajedno uz obični grab, pitomi kesten ili bukvu. Raste od nizina do 1300 m nadmorske visine. Razmnožava se sjemenom koje brzo klija. Skromnih je zahtjeva prema staništu, odgovaraju mu svježa zemljišta, slabije uspijeva na tlu kisele reakcije.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica od 100-140cm
+- Sadnice se prodaju golog korijena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
+- Ne stvara alergene.
+- Atraktivno listopadno stablo poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
+- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, i odgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica od 40-60cm
+- Sadnice se prodaju golog korijena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+- Sadnice s biljnom putovnicom i potvrdom zdravstvene ispravnosti
+Opis vrste:
+- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
+- Ne stvara alergene.
+- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
+- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, i odgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
+  </si>
+  <si>
+    <t>Informacije o sadnicama:
+- Visina sadnica od 70-100cm
+- Sadnice se prodaju golog korijena
+- Sadnja tijekom mirovanja vegetacije (listopad-travanj)
+Opis vrste:
+- Uzgojni oblik: ukrasno stablo, sa bujnom, velikom krošnjom.
+- Ne stvara alergene.
+- Atraktivno listopadno stablo  poznato po svom brzom rastu i predivnoj crvenoj boji lišća u jesen.
+- Stanište: Otporno je stablo na niske temperature i gradska onečišćenja. Relativno je brzog rasta, podnosi sjenu, tolerira većinu tla, uspijeva i na siromašnim zemljištima i tlima kisele reakcije, i odgovara mu pjeskovito i svježe tlo. Ne podnosi poplavljena ali i suha staništa.</t>
   </si>
 </sst>
 </file>
@@ -900,7 +900,7 @@
         <v>56</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>47</v>
@@ -920,7 +920,7 @@
         <v>57</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>44</v>
@@ -940,7 +940,7 @@
         <v>64</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>60</v>
@@ -960,7 +960,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>48</v>
@@ -980,7 +980,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>49</v>
@@ -1000,7 +1000,7 @@
         <v>19</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>70</v>
